--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5395,6 +5395,637 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118753340</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90797</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>574381</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7173106</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>118752989</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>574381</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7173106</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118755595</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>574298</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7173055</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118755013</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>574518</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7173188</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118755675</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>574263</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7173022</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118754580</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>574518</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7173188</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118753340</v>
+        <v>118753407</v>
       </c>
       <c r="B45" t="n">
-        <v>90797</v>
+        <v>78647</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118752989</v>
+        <v>118754580</v>
       </c>
       <c r="B46" t="n">
-        <v>78646</v>
+        <v>78647</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R46" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5604,7 +5604,7 @@
         <v>118755595</v>
       </c>
       <c r="B47" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>118755013</v>
       </c>
       <c r="B48" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755675</v>
+        <v>118753340</v>
       </c>
       <c r="B49" t="n">
-        <v>79726</v>
+        <v>90807</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,40 +5821,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574263</v>
+        <v>574381</v>
       </c>
       <c r="R49" t="n">
-        <v>7173022</v>
+        <v>7173106</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5892,24 +5889,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5926,10 +5907,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118754580</v>
+        <v>118755675</v>
       </c>
       <c r="B50" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5942,37 +5923,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R50" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6010,8 +5994,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,7 +5397,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118753407</v>
+        <v>118752989</v>
       </c>
       <c r="B45" t="n">
         <v>78647</v>
@@ -5499,7 +5499,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118754580</v>
+        <v>118754133</v>
       </c>
       <c r="B46" t="n">
         <v>78647</v>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118755595</v>
+        <v>118753340</v>
       </c>
       <c r="B47" t="n">
-        <v>79727</v>
+        <v>90807</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,13 +5641,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R47" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118753340</v>
+        <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>90807</v>
+        <v>79727</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,37 +5821,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574381</v>
+        <v>574263</v>
       </c>
       <c r="R49" t="n">
-        <v>7173106</v>
+        <v>7173022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5889,8 +5892,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5907,7 +5926,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755675</v>
+        <v>118755595</v>
       </c>
       <c r="B50" t="n">
         <v>79727</v>
@@ -5941,19 +5960,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574263</v>
+        <v>574298</v>
       </c>
       <c r="R50" t="n">
-        <v>7173022</v>
+        <v>7173055</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5994,24 +6010,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118752989</v>
+        <v>118753340</v>
       </c>
       <c r="B45" t="n">
-        <v>78647</v>
+        <v>90819</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5502,7 +5502,7 @@
         <v>118754133</v>
       </c>
       <c r="B46" t="n">
-        <v>78647</v>
+        <v>78652</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753340</v>
+        <v>118753407</v>
       </c>
       <c r="B47" t="n">
-        <v>90807</v>
+        <v>78652</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755013</v>
+        <v>118755595</v>
       </c>
       <c r="B48" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R48" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755595</v>
+        <v>118755013</v>
       </c>
       <c r="B50" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5966,13 +5966,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574298</v>
+        <v>574518</v>
       </c>
       <c r="R50" t="n">
-        <v>7173055</v>
+        <v>7173188</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118753340</v>
+        <v>118755013</v>
       </c>
       <c r="B45" t="n">
-        <v>90819</v>
+        <v>79732</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R45" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118754133</v>
+        <v>118755595</v>
       </c>
       <c r="B46" t="n">
-        <v>78652</v>
+        <v>79732</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5539,13 +5539,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R46" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755595</v>
+        <v>118753340</v>
       </c>
       <c r="B48" t="n">
-        <v>79732</v>
+        <v>90826</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5719,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R48" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755675</v>
+        <v>118754580</v>
       </c>
       <c r="B49" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,40 +5821,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574263</v>
+        <v>574518</v>
       </c>
       <c r="R49" t="n">
-        <v>7173022</v>
+        <v>7173188</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5892,24 +5889,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5926,7 +5907,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755013</v>
+        <v>118755675</v>
       </c>
       <c r="B50" t="n">
         <v>79732</v>
@@ -5960,19 +5941,22 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R50" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6010,8 +5994,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118755013</v>
+        <v>118755595</v>
       </c>
       <c r="B45" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5415,11 +5415,6 @@
       <c r="E45" t="n">
         <v>6458</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5437,13 +5432,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R45" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5499,10 +5494,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118755595</v>
+        <v>118752989</v>
       </c>
       <c r="B46" t="n">
-        <v>79732</v>
+        <v>78653</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5510,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>230405</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5539,13 +5529,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R46" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5601,10 +5591,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753407</v>
+        <v>118753340</v>
       </c>
       <c r="B47" t="n">
-        <v>78652</v>
+        <v>90831</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5607,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5703,10 +5688,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118753340</v>
+        <v>118755675</v>
       </c>
       <c r="B48" t="n">
-        <v>90826</v>
+        <v>79733</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,37 +5704,35 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574381</v>
+        <v>574263</v>
       </c>
       <c r="R48" t="n">
-        <v>7173106</v>
+        <v>7173022</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5787,8 +5770,19 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5805,10 +5799,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118754580</v>
+        <v>118754133</v>
       </c>
       <c r="B49" t="n">
-        <v>78652</v>
+        <v>78653</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5822,11 +5816,6 @@
       </c>
       <c r="E49" t="n">
         <v>230405</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5907,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755675</v>
+        <v>118755013</v>
       </c>
       <c r="B50" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5925,11 +5914,6 @@
       <c r="E50" t="n">
         <v>6458</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5941,22 +5925,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574263</v>
+        <v>574518</v>
       </c>
       <c r="R50" t="n">
-        <v>7173022</v>
+        <v>7173188</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5994,24 +5975,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5799,10 +5799,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118754133</v>
+        <v>118755013</v>
       </c>
       <c r="B49" t="n">
-        <v>78653</v>
+        <v>79733</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5815,16 +5815,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755013</v>
+        <v>118754133</v>
       </c>
       <c r="B50" t="n">
-        <v>79733</v>
+        <v>78653</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5912,16 +5912,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>118755595</v>
       </c>
       <c r="B45" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5414,6 +5414,11 @@
       </c>
       <c r="E45" t="n">
         <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5494,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118752989</v>
+        <v>118755013</v>
       </c>
       <c r="B46" t="n">
-        <v>78653</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5510,16 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5529,10 +5539,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R46" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5591,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753340</v>
+        <v>118754133</v>
       </c>
       <c r="B47" t="n">
-        <v>90831</v>
+        <v>78657</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5607,16 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>230405</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5626,10 +5641,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R47" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5688,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755675</v>
+        <v>118753407</v>
       </c>
       <c r="B48" t="n">
-        <v>79733</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5704,35 +5719,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>230405</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574263</v>
+        <v>574381</v>
       </c>
       <c r="R48" t="n">
-        <v>7173022</v>
+        <v>7173106</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5770,19 +5787,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5799,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755013</v>
+        <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5817,6 +5823,11 @@
       <c r="E49" t="n">
         <v>6458</v>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5828,19 +5839,22 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R49" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5878,8 +5892,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5896,10 +5926,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118754133</v>
+        <v>118753340</v>
       </c>
       <c r="B50" t="n">
-        <v>78653</v>
+        <v>90844</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5912,16 +5942,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>230405</v>
+        <v>5432</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5931,10 +5966,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R50" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118755595</v>
+        <v>118754133</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574298</v>
+        <v>574518</v>
       </c>
       <c r="R45" t="n">
-        <v>7173055</v>
+        <v>7173188</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118755013</v>
+        <v>118755675</v>
       </c>
       <c r="B46" t="n">
         <v>79737</v>
@@ -5533,19 +5533,22 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R46" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5583,8 +5586,24 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5601,7 +5620,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118754133</v>
+        <v>118752989</v>
       </c>
       <c r="B47" t="n">
         <v>78657</v>
@@ -5641,10 +5660,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R47" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,10 +5722,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118753407</v>
+        <v>118753340</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>90857</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5738,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5805,7 +5824,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755675</v>
+        <v>118755595</v>
       </c>
       <c r="B49" t="n">
         <v>79737</v>
@@ -5839,19 +5858,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574263</v>
+        <v>574298</v>
       </c>
       <c r="R49" t="n">
-        <v>7173022</v>
+        <v>7173055</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5892,24 +5908,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5926,10 +5926,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118753340</v>
+        <v>118755013</v>
       </c>
       <c r="B50" t="n">
-        <v>90844</v>
+        <v>79737</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R50" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118754133</v>
+        <v>118755675</v>
       </c>
       <c r="B45" t="n">
-        <v>78657</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,37 +5413,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R45" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5481,8 +5484,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5499,10 +5518,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118755675</v>
+        <v>118753407</v>
       </c>
       <c r="B46" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,40 +5534,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574263</v>
+        <v>574381</v>
       </c>
       <c r="R46" t="n">
-        <v>7173022</v>
+        <v>7173106</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5586,24 +5602,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5620,10 +5620,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118752989</v>
+        <v>118753340</v>
       </c>
       <c r="B47" t="n">
-        <v>78657</v>
+        <v>90857</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5636,21 +5636,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5722,10 +5722,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118753340</v>
+        <v>118755013</v>
       </c>
       <c r="B48" t="n">
-        <v>90857</v>
+        <v>79737</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5738,21 +5738,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R48" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5824,10 +5824,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755595</v>
+        <v>118754133</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5840,21 +5840,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5864,13 +5864,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574298</v>
+        <v>574518</v>
       </c>
       <c r="R49" t="n">
-        <v>7173055</v>
+        <v>7173188</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755013</v>
+        <v>118755595</v>
       </c>
       <c r="B50" t="n">
         <v>79737</v>
@@ -5966,13 +5966,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R50" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,7 +5397,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118755675</v>
+        <v>118755013</v>
       </c>
       <c r="B45" t="n">
         <v>79737</v>
@@ -5431,22 +5431,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574263</v>
+        <v>574518</v>
       </c>
       <c r="R45" t="n">
-        <v>7173022</v>
+        <v>7173188</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5484,24 +5481,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5518,7 +5499,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118753407</v>
+        <v>118754133</v>
       </c>
       <c r="B46" t="n">
         <v>78657</v>
@@ -5558,10 +5539,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R46" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5620,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753340</v>
+        <v>118752989</v>
       </c>
       <c r="B47" t="n">
-        <v>90857</v>
+        <v>78657</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5636,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5722,7 +5703,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755013</v>
+        <v>118755595</v>
       </c>
       <c r="B48" t="n">
         <v>79737</v>
@@ -5762,13 +5743,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R48" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5824,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118754133</v>
+        <v>118753340</v>
       </c>
       <c r="B49" t="n">
-        <v>78657</v>
+        <v>90851</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5840,21 +5821,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5864,10 +5845,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R49" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5926,7 +5907,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755595</v>
+        <v>118755675</v>
       </c>
       <c r="B50" t="n">
         <v>79737</v>
@@ -5960,16 +5941,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574298</v>
+        <v>574263</v>
       </c>
       <c r="R50" t="n">
-        <v>7173055</v>
+        <v>7173022</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6010,8 +5994,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118754133</v>
+        <v>118753340</v>
       </c>
       <c r="B46" t="n">
-        <v>78657</v>
+        <v>90851</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R46" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118752989</v>
+        <v>118754580</v>
       </c>
       <c r="B47" t="n">
         <v>78657</v>
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R47" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755595</v>
+        <v>118753407</v>
       </c>
       <c r="B48" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5719,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R48" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118753340</v>
+        <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>90851</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,37 +5821,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574381</v>
+        <v>574263</v>
       </c>
       <c r="R49" t="n">
-        <v>7173106</v>
+        <v>7173022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5889,8 +5892,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5907,7 +5926,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755675</v>
+        <v>118755595</v>
       </c>
       <c r="B50" t="n">
         <v>79737</v>
@@ -5941,19 +5960,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574263</v>
+        <v>574298</v>
       </c>
       <c r="R50" t="n">
-        <v>7173022</v>
+        <v>7173055</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5994,24 +6010,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118755013</v>
+        <v>118754133</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>78658</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118753340</v>
+        <v>118753407</v>
       </c>
       <c r="B46" t="n">
-        <v>90851</v>
+        <v>78658</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118754580</v>
+        <v>118753340</v>
       </c>
       <c r="B47" t="n">
-        <v>78657</v>
+        <v>90852</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R47" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118753407</v>
+        <v>118755013</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>79738</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5719,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R48" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755675</v>
+        <v>118755595</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5839,19 +5839,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574263</v>
+        <v>574298</v>
       </c>
       <c r="R49" t="n">
-        <v>7173022</v>
+        <v>7173055</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5892,24 +5889,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5926,10 +5907,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755595</v>
+        <v>118755675</v>
       </c>
       <c r="B50" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5960,16 +5941,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574298</v>
+        <v>574263</v>
       </c>
       <c r="R50" t="n">
-        <v>7173055</v>
+        <v>7173022</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6010,8 +5994,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118754133</v>
+        <v>118754580</v>
       </c>
       <c r="B45" t="n">
-        <v>78658</v>
+        <v>78661</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118753407</v>
+        <v>118755595</v>
       </c>
       <c r="B46" t="n">
-        <v>78658</v>
+        <v>79741</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5539,13 +5539,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574381</v>
+        <v>574298</v>
       </c>
       <c r="R46" t="n">
-        <v>7173106</v>
+        <v>7173055</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753340</v>
+        <v>118753407</v>
       </c>
       <c r="B47" t="n">
-        <v>90852</v>
+        <v>78661</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5706,7 +5706,7 @@
         <v>118755013</v>
       </c>
       <c r="B48" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755595</v>
+        <v>118753340</v>
       </c>
       <c r="B49" t="n">
-        <v>79738</v>
+        <v>90855</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,21 +5821,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5845,13 +5845,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R49" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>118755675</v>
       </c>
       <c r="B50" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -5397,7 +5397,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118754580</v>
+        <v>118753407</v>
       </c>
       <c r="B45" t="n">
         <v>78661</v>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R45" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753407</v>
+        <v>118755013</v>
       </c>
       <c r="B47" t="n">
-        <v>78661</v>
+        <v>79741</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R47" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755013</v>
+        <v>118754133</v>
       </c>
       <c r="B48" t="n">
-        <v>79741</v>
+        <v>78661</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5719,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118753340</v>
+        <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>90855</v>
+        <v>79741</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,37 +5821,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574381</v>
+        <v>574263</v>
       </c>
       <c r="R49" t="n">
-        <v>7173106</v>
+        <v>7173022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5889,8 +5892,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5907,10 +5926,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755675</v>
+        <v>118753340</v>
       </c>
       <c r="B50" t="n">
-        <v>79741</v>
+        <v>90855</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5923,40 +5942,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574263</v>
+        <v>574381</v>
       </c>
       <c r="R50" t="n">
-        <v>7173022</v>
+        <v>7173106</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5994,24 +6010,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 46776-2024 artfynd.xlsx
+++ b/artfynd/A 46776-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97710181</v>
+        <v>119536511</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574384.3140236223</v>
+        <v>574477</v>
       </c>
       <c r="R2" t="n">
-        <v>7173046.907611273</v>
+        <v>7173211</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-12-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-12-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97709971</v>
+        <v>119537750</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,38 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574373.3642706776</v>
+        <v>574478</v>
       </c>
       <c r="R3" t="n">
-        <v>7173125.891344385</v>
+        <v>7173200</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-12-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-12-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98478782</v>
+        <v>119536751</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,35 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574285.5542711127</v>
+        <v>574483</v>
       </c>
       <c r="R4" t="n">
-        <v>7173033.770365979</v>
+        <v>7173213</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,22 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119537765</v>
+        <v>118753880</v>
       </c>
       <c r="B5" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574394</v>
+        <v>574429</v>
       </c>
       <c r="R5" t="n">
-        <v>7173055</v>
+        <v>7173158</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,27 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536050</v>
+        <v>119536013</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,39 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574276</v>
+        <v>574482</v>
       </c>
       <c r="R6" t="n">
-        <v>7173028</v>
+        <v>7173212</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,7 +1153,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1163,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119537755</v>
+        <v>119536014</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,37 +1201,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574478</v>
+        <v>574494</v>
       </c>
       <c r="R7" t="n">
-        <v>7173200</v>
+        <v>7173176</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1258,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,6 +1282,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1328,22 +1294,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119537764</v>
+        <v>119536015</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,37 +1312,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574381</v>
+        <v>574453</v>
       </c>
       <c r="R8" t="n">
-        <v>7173062</v>
+        <v>7173174</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,12 +1366,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,22 +1401,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537018</v>
+        <v>119537753</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,37 +1419,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574304</v>
+        <v>574485</v>
       </c>
       <c r="R9" t="n">
-        <v>7173084</v>
+        <v>7173191</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,22 +1473,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,60 +1498,55 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536650</v>
+        <v>119537765</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574299</v>
+        <v>574394</v>
       </c>
       <c r="R10" t="n">
-        <v>7173057</v>
+        <v>7173055</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1619,22 +1570,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,44 +1595,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536288</v>
+        <v>119536410</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>2062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574304</v>
+        <v>574478</v>
       </c>
       <c r="R11" t="n">
-        <v>7173083</v>
+        <v>7173213</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,7 +1672,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1746,7 +1682,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>S. Str</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,6 +1698,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1773,15 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536051</v>
+        <v>119536396</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,39 +1740,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574493</v>
+        <v>574301</v>
       </c>
       <c r="R12" t="n">
-        <v>7173176</v>
+        <v>7173058</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1853,7 +1799,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1809,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,15 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536704</v>
+        <v>119536452</v>
       </c>
       <c r="B13" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,16 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>4366</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574517</v>
+        <v>574298</v>
       </c>
       <c r="R13" t="n">
-        <v>7173204</v>
+        <v>7172996</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1960,7 +1906,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1916,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,15 +1943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537741</v>
+        <v>119535961</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,37 +1954,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574317</v>
+        <v>574445</v>
       </c>
       <c r="R14" t="n">
-        <v>7173030</v>
+        <v>7173171</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,12 +2008,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,60 +2043,56 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537750</v>
+        <v>97709971</v>
       </c>
       <c r="B15" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574478</v>
+        <v>574374</v>
       </c>
       <c r="R15" t="n">
-        <v>7173200</v>
+        <v>7173126</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,12 +2116,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2021-12-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2021-12-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,27 +2136,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536410</v>
+        <v>119537016</v>
       </c>
       <c r="B16" t="n">
-        <v>90905</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2241,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574478</v>
+        <v>574275</v>
       </c>
       <c r="R16" t="n">
-        <v>7173213</v>
+        <v>7173029</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2276,7 +2218,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2286,12 +2228,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>S. Str</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,21 +2239,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2333,37 +2255,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119535961</v>
+        <v>119537017</v>
       </c>
       <c r="B17" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2373,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574445</v>
+        <v>574299</v>
       </c>
       <c r="R17" t="n">
-        <v>7173171</v>
+        <v>7173057</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2408,7 +2325,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2335,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,19 +2362,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119537016</v>
+        <v>119537018</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2485,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574275</v>
+        <v>574304</v>
       </c>
       <c r="R18" t="n">
-        <v>7173029</v>
+        <v>7173084</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2520,7 +2432,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2442,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,19 +2469,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119537773</v>
+        <v>119537019</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2593,17 +2500,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574368</v>
+        <v>574304</v>
       </c>
       <c r="R19" t="n">
-        <v>7172978</v>
+        <v>7173083</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,12 +2534,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,60 +2569,55 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119537761</v>
+        <v>119537020</v>
       </c>
       <c r="B20" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574382</v>
+        <v>574470</v>
       </c>
       <c r="R20" t="n">
-        <v>7173106</v>
+        <v>7173208</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2729,12 +2641,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,26 +2676,21 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119537017</v>
+        <v>119537021</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2801,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574299</v>
+        <v>574516</v>
       </c>
       <c r="R21" t="n">
-        <v>7173057</v>
+        <v>7173204</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2836,7 +2753,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,7 +2763,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,19 +2790,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119537020</v>
+        <v>119537022</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2913,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574470</v>
+        <v>574492</v>
       </c>
       <c r="R22" t="n">
-        <v>7173208</v>
+        <v>7173175</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2948,7 +2860,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2958,7 +2870,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,53 +2897,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536452</v>
+        <v>119537741</v>
       </c>
       <c r="B23" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574298</v>
+        <v>574317</v>
       </c>
       <c r="R23" t="n">
-        <v>7172996</v>
+        <v>7173030</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3055,22 +2962,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,44 +2987,39 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119537740</v>
+        <v>119537742</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3137,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574317</v>
+        <v>574381</v>
       </c>
       <c r="R24" t="n">
-        <v>7173030</v>
+        <v>7173062</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3199,53 +3091,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536651</v>
+        <v>119537746</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574475</v>
+        <v>574574</v>
       </c>
       <c r="R25" t="n">
-        <v>7173208</v>
+        <v>7173271</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3269,22 +3156,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>19:53</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>19:53</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3304,66 +3181,52 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119537744</v>
+        <v>119537748</v>
       </c>
       <c r="B26" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574625</v>
+        <v>574478</v>
       </c>
       <c r="R26" t="n">
-        <v>7173279</v>
+        <v>7173200</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3422,19 +3285,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119537022</v>
+        <v>119537759</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3458,17 +3316,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574492</v>
+        <v>574364</v>
       </c>
       <c r="R27" t="n">
-        <v>7173175</v>
+        <v>7173153</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3492,22 +3350,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3527,26 +3375,21 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537771</v>
+        <v>119537766</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3574,10 +3417,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574350</v>
+        <v>574395</v>
       </c>
       <c r="R28" t="n">
-        <v>7173009</v>
+        <v>7173021</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3636,53 +3479,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536511</v>
+        <v>119537769</v>
       </c>
       <c r="B29" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574477</v>
+        <v>574386</v>
       </c>
       <c r="R29" t="n">
-        <v>7173211</v>
+        <v>7173013</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3706,22 +3544,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>19:57</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>19:57</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3741,26 +3569,21 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119537746</v>
+        <v>119537771</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3788,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574574</v>
+        <v>574350</v>
       </c>
       <c r="R30" t="n">
-        <v>7173271</v>
+        <v>7173009</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3850,58 +3673,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536053</v>
+        <v>119537773</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574455</v>
+        <v>574368</v>
       </c>
       <c r="R31" t="n">
-        <v>7173175</v>
+        <v>7172978</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3925,22 +3738,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>20:27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>20:27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3960,22 +3763,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536014</v>
+        <v>119536719</v>
       </c>
       <c r="B32" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3983,37 +3781,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574494</v>
+        <v>574406</v>
       </c>
       <c r="R32" t="n">
-        <v>7173176</v>
+        <v>7173206</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4045,7 +3840,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4055,7 +3850,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4064,7 +3859,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4083,53 +3877,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536242</v>
+        <v>119537761</v>
       </c>
       <c r="B33" t="n">
-        <v>90067</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>256703</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574298</v>
+        <v>574382</v>
       </c>
       <c r="R33" t="n">
-        <v>7172996</v>
+        <v>7173106</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4153,22 +3942,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4188,22 +3967,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536396</v>
+        <v>119535990</v>
       </c>
       <c r="B34" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4211,21 +3985,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4235,10 +4009,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574301</v>
+        <v>574331</v>
       </c>
       <c r="R34" t="n">
-        <v>7173058</v>
+        <v>7173100</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4270,7 +4044,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4280,7 +4054,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4307,15 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119537753</v>
+        <v>97710181</v>
       </c>
       <c r="B35" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4323,37 +4092,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574485</v>
+        <v>574384</v>
       </c>
       <c r="R35" t="n">
-        <v>7173191</v>
+        <v>7173046</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4377,12 +4147,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2021-12-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2021-12-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4397,27 +4167,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119535990</v>
+        <v>98478782</v>
       </c>
       <c r="B36" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4425,34 +4190,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574331</v>
+        <v>574286</v>
       </c>
       <c r="R36" t="n">
-        <v>7173100</v>
+        <v>7173034</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4479,22 +4245,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>19:17</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>19:17</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4509,27 +4265,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536751</v>
+        <v>118755013</v>
       </c>
       <c r="B37" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4537,37 +4288,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574483</v>
+        <v>574518</v>
       </c>
       <c r="R37" t="n">
-        <v>7173213</v>
+        <v>7173188</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4591,22 +4342,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>20:07</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>20:07</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4621,27 +4362,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119537769</v>
+        <v>118755595</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4649,34 +4385,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574386</v>
+        <v>574298</v>
       </c>
       <c r="R38" t="n">
-        <v>7173013</v>
+        <v>7173055</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,27 +4459,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536013</v>
+        <v>118755675</v>
       </c>
       <c r="B39" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4751,37 +4482,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574482</v>
+        <v>574263</v>
       </c>
       <c r="R39" t="n">
-        <v>7173212</v>
+        <v>7173022</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4805,22 +4539,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>19:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>19:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4829,18 +4553,34 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4850,12 +4590,7 @@
         <v>119536649</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4959,15 +4694,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119537767</v>
+        <v>119536650</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4975,37 +4705,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574395</v>
+        <v>574299</v>
       </c>
       <c r="R41" t="n">
-        <v>7173021</v>
+        <v>7173057</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5029,12 +4759,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5054,22 +4794,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119537021</v>
+        <v>119536651</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5077,21 +4812,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5101,10 +4836,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574516</v>
+        <v>574475</v>
       </c>
       <c r="R42" t="n">
-        <v>7173204</v>
+        <v>7173208</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5136,7 +4871,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5146,7 +4881,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5173,15 +4908,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119537019</v>
+        <v>119537740</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5189,37 +4919,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574304</v>
+        <v>574317</v>
       </c>
       <c r="R43" t="n">
-        <v>7173083</v>
+        <v>7173030</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5243,22 +4973,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>19:12</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>19:12</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5278,44 +4998,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536015</v>
+        <v>119536288</v>
       </c>
       <c r="B44" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5325,10 +5040,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574453</v>
+        <v>574304</v>
       </c>
       <c r="R44" t="n">
-        <v>7173174</v>
+        <v>7173083</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5360,7 +5075,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5370,7 +5085,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,15 +5112,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118753407</v>
+        <v>119536050</v>
       </c>
       <c r="B45" t="n">
-        <v>78661</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5413,37 +5123,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574381</v>
+        <v>574276</v>
       </c>
       <c r="R45" t="n">
-        <v>7173106</v>
+        <v>7173028</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5467,12 +5182,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5487,27 +5212,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118755595</v>
+        <v>119536051</v>
       </c>
       <c r="B46" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5515,37 +5235,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574298</v>
+        <v>574493</v>
       </c>
       <c r="R46" t="n">
-        <v>7173055</v>
+        <v>7173176</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5569,12 +5294,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5589,27 +5324,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118755013</v>
+        <v>119536053</v>
       </c>
       <c r="B47" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5617,37 +5347,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574518</v>
+        <v>574455</v>
       </c>
       <c r="R47" t="n">
-        <v>7173188</v>
+        <v>7173175</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5671,12 +5406,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5691,65 +5436,69 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118754133</v>
+        <v>119537744</v>
       </c>
       <c r="B48" t="n">
-        <v>78661</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574518</v>
+        <v>574625</v>
       </c>
       <c r="R48" t="n">
-        <v>7173188</v>
+        <v>7173279</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5793,68 +5542,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755675</v>
+        <v>119536296</v>
       </c>
       <c r="B49" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574263</v>
+        <v>574412</v>
       </c>
       <c r="R49" t="n">
-        <v>7173022</v>
+        <v>7173113</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5878,12 +5619,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5892,87 +5643,66 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118753340</v>
+        <v>119537763</v>
       </c>
       <c r="B50" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574381</v>
+        <v>574401</v>
       </c>
       <c r="R50" t="n">
-        <v>7173106</v>
+        <v>7173101</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6016,15 +5746,520 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118752989</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>574381</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7173106</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
           <t>Louise Karlsson</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>Louise Karlsson</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>118753921</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>574429</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7173158</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118754133</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>574518</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7173188</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>119536242</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>574298</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7172996</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>119536704</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>574517</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7173204</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
